--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ133"/>
+  <dimension ref="A1:AZ156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,48 +786,57 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129215841</v>
+        <v>137044520</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92136</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>434433</v>
+        <v>434065</v>
       </c>
       <c r="R3" t="n">
-        <v>6806597</v>
+        <v>6806539</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,12 +860,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -865,31 +884,40 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215841</t>
+          <t>https://artportalen.se/Sighting/137044520</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129215843</v>
+        <v>129215841</v>
       </c>
       <c r="B4" t="n">
         <v>79327</v>
@@ -924,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>434628</v>
+        <v>434433</v>
       </c>
       <c r="R4" t="n">
-        <v>6806457</v>
+        <v>6806597</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +996,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -985,13 +1014,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215843</t>
+          <t>https://artportalen.se/Sighting/129215841</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129215844</v>
+        <v>129215843</v>
       </c>
       <c r="B5" t="n">
         <v>79327</v>
@@ -1026,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>434623</v>
+        <v>434628</v>
       </c>
       <c r="R5" t="n">
-        <v>6806466</v>
+        <v>6806457</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,13 +1116,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215844</t>
+          <t>https://artportalen.se/Sighting/129215843</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129215845</v>
+        <v>129215844</v>
       </c>
       <c r="B6" t="n">
         <v>79327</v>
@@ -1128,10 +1157,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>434585</v>
+        <v>434623</v>
       </c>
       <c r="R6" t="n">
-        <v>6806500</v>
+        <v>6806466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,13 +1218,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215845</t>
+          <t>https://artportalen.se/Sighting/129215844</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129215846</v>
+        <v>129215845</v>
       </c>
       <c r="B7" t="n">
         <v>79327</v>
@@ -1230,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>434523</v>
+        <v>434585</v>
       </c>
       <c r="R7" t="n">
-        <v>6806496</v>
+        <v>6806500</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,13 +1320,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215846</t>
+          <t>https://artportalen.se/Sighting/129215845</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129215847</v>
+        <v>129215846</v>
       </c>
       <c r="B8" t="n">
         <v>79327</v>
@@ -1335,7 +1364,7 @@
         <v>434523</v>
       </c>
       <c r="R8" t="n">
-        <v>6806508</v>
+        <v>6806496</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,13 +1422,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215847</t>
+          <t>https://artportalen.se/Sighting/129215846</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129215848</v>
+        <v>129215847</v>
       </c>
       <c r="B9" t="n">
         <v>79327</v>
@@ -1434,10 +1463,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>434473</v>
+        <v>434523</v>
       </c>
       <c r="R9" t="n">
-        <v>6806453</v>
+        <v>6806508</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,13 +1524,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215848</t>
+          <t>https://artportalen.se/Sighting/129215847</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129215849</v>
+        <v>129215848</v>
       </c>
       <c r="B10" t="n">
         <v>79327</v>
@@ -1536,10 +1565,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>434437</v>
+        <v>434473</v>
       </c>
       <c r="R10" t="n">
-        <v>6806501</v>
+        <v>6806453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,13 +1626,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215849</t>
+          <t>https://artportalen.se/Sighting/129215848</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129215850</v>
+        <v>129215849</v>
       </c>
       <c r="B11" t="n">
         <v>79327</v>
@@ -1638,10 +1667,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>434376</v>
+        <v>434437</v>
       </c>
       <c r="R11" t="n">
-        <v>6806560</v>
+        <v>6806501</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,13 +1728,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215850</t>
+          <t>https://artportalen.se/Sighting/129215849</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129215851</v>
+        <v>129215850</v>
       </c>
       <c r="B12" t="n">
         <v>79327</v>
@@ -1740,10 +1769,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>434362</v>
+        <v>434376</v>
       </c>
       <c r="R12" t="n">
-        <v>6806519</v>
+        <v>6806560</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,13 +1830,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215851</t>
+          <t>https://artportalen.se/Sighting/129215850</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129215852</v>
+        <v>129215851</v>
       </c>
       <c r="B13" t="n">
         <v>79327</v>
@@ -1842,10 +1871,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>434335</v>
+        <v>434362</v>
       </c>
       <c r="R13" t="n">
-        <v>6806532</v>
+        <v>6806519</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1903,13 +1932,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215852</t>
+          <t>https://artportalen.se/Sighting/129215851</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129215853</v>
+        <v>129215852</v>
       </c>
       <c r="B14" t="n">
         <v>79327</v>
@@ -1944,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>434280</v>
+        <v>434335</v>
       </c>
       <c r="R14" t="n">
-        <v>6806556</v>
+        <v>6806532</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2005,13 +2034,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215853</t>
+          <t>https://artportalen.se/Sighting/129215852</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129215854</v>
+        <v>129215853</v>
       </c>
       <c r="B15" t="n">
         <v>79327</v>
@@ -2046,10 +2075,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>434268</v>
+        <v>434280</v>
       </c>
       <c r="R15" t="n">
-        <v>6806557</v>
+        <v>6806556</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2107,13 +2136,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215854</t>
+          <t>https://artportalen.se/Sighting/129215853</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129215856</v>
+        <v>129215854</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2148,10 +2177,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>434194</v>
+        <v>434268</v>
       </c>
       <c r="R16" t="n">
-        <v>6806560</v>
+        <v>6806557</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,13 +2238,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215856</t>
+          <t>https://artportalen.se/Sighting/129215854</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129215857</v>
+        <v>129215856</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2250,10 +2279,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>434179</v>
+        <v>434194</v>
       </c>
       <c r="R17" t="n">
-        <v>6806557</v>
+        <v>6806560</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,13 +2340,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215857</t>
+          <t>https://artportalen.se/Sighting/129215856</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129215858</v>
+        <v>129215857</v>
       </c>
       <c r="B18" t="n">
         <v>79327</v>
@@ -2352,10 +2381,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>434135</v>
+        <v>434179</v>
       </c>
       <c r="R18" t="n">
-        <v>6806556</v>
+        <v>6806557</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,13 +2442,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215858</t>
+          <t>https://artportalen.se/Sighting/129215857</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129215859</v>
+        <v>129215858</v>
       </c>
       <c r="B19" t="n">
         <v>79327</v>
@@ -2454,10 +2483,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>434177</v>
+        <v>434135</v>
       </c>
       <c r="R19" t="n">
-        <v>6806592</v>
+        <v>6806556</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,13 +2544,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215859</t>
+          <t>https://artportalen.se/Sighting/129215858</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129215860</v>
+        <v>129215859</v>
       </c>
       <c r="B20" t="n">
         <v>79327</v>
@@ -2556,10 +2585,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>434241</v>
+        <v>434177</v>
       </c>
       <c r="R20" t="n">
-        <v>6806618</v>
+        <v>6806592</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2617,13 +2646,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215860</t>
+          <t>https://artportalen.se/Sighting/129215859</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129215861</v>
+        <v>129215860</v>
       </c>
       <c r="B21" t="n">
         <v>79327</v>
@@ -2652,19 +2681,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>434259</v>
+        <v>434241</v>
       </c>
       <c r="R21" t="n">
-        <v>6806607</v>
+        <v>6806618</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,7 +2731,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2723,13 +2748,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215861</t>
+          <t>https://artportalen.se/Sighting/129215860</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129215862</v>
+        <v>129215861</v>
       </c>
       <c r="B22" t="n">
         <v>79327</v>
@@ -2758,16 +2783,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>434270</v>
+        <v>434259</v>
       </c>
       <c r="R22" t="n">
-        <v>6806602</v>
+        <v>6806607</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2808,6 +2836,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2825,13 +2854,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215862</t>
+          <t>https://artportalen.se/Sighting/129215861</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129215863</v>
+        <v>129215862</v>
       </c>
       <c r="B23" t="n">
         <v>79327</v>
@@ -2866,10 +2895,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>434279</v>
+        <v>434270</v>
       </c>
       <c r="R23" t="n">
-        <v>6806587</v>
+        <v>6806602</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,13 +2956,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215863</t>
+          <t>https://artportalen.se/Sighting/129215862</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129215864</v>
+        <v>129215863</v>
       </c>
       <c r="B24" t="n">
         <v>79327</v>
@@ -2968,10 +2997,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>434319</v>
+        <v>434279</v>
       </c>
       <c r="R24" t="n">
-        <v>6806589</v>
+        <v>6806587</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,13 +3058,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215864</t>
+          <t>https://artportalen.se/Sighting/129215863</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129215865</v>
+        <v>129215864</v>
       </c>
       <c r="B25" t="n">
         <v>79327</v>
@@ -3070,10 +3099,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>434358</v>
+        <v>434319</v>
       </c>
       <c r="R25" t="n">
-        <v>6806608</v>
+        <v>6806589</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3131,13 +3160,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215865</t>
+          <t>https://artportalen.se/Sighting/129215864</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129215867</v>
+        <v>129215865</v>
       </c>
       <c r="B26" t="n">
         <v>79327</v>
@@ -3172,10 +3201,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>434375</v>
+        <v>434358</v>
       </c>
       <c r="R26" t="n">
-        <v>6806574</v>
+        <v>6806608</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3233,13 +3262,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215867</t>
+          <t>https://artportalen.se/Sighting/129215865</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129215868</v>
+        <v>129215867</v>
       </c>
       <c r="B27" t="n">
         <v>79327</v>
@@ -3274,10 +3303,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>434415</v>
+        <v>434375</v>
       </c>
       <c r="R27" t="n">
-        <v>6806576</v>
+        <v>6806574</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3335,13 +3364,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215868</t>
+          <t>https://artportalen.se/Sighting/129215867</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129215869</v>
+        <v>129215868</v>
       </c>
       <c r="B28" t="n">
         <v>79327</v>
@@ -3376,10 +3405,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>434432</v>
+        <v>434415</v>
       </c>
       <c r="R28" t="n">
-        <v>6806606</v>
+        <v>6806576</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3437,13 +3466,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215869</t>
+          <t>https://artportalen.se/Sighting/129215868</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129215871</v>
+        <v>129215869</v>
       </c>
       <c r="B29" t="n">
         <v>79327</v>
@@ -3478,10 +3507,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>434443</v>
+        <v>434432</v>
       </c>
       <c r="R29" t="n">
-        <v>6806595</v>
+        <v>6806606</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3539,13 +3568,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215871</t>
+          <t>https://artportalen.se/Sighting/129215869</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129215872</v>
+        <v>129215871</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3574,19 +3603,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>434454</v>
+        <v>434443</v>
       </c>
       <c r="R30" t="n">
-        <v>6806619</v>
+        <v>6806595</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3627,7 +3653,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3645,13 +3670,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215872</t>
+          <t>https://artportalen.se/Sighting/129215871</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129215873</v>
+        <v>129215872</v>
       </c>
       <c r="B31" t="n">
         <v>79327</v>
@@ -3680,16 +3705,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>434463</v>
+        <v>434454</v>
       </c>
       <c r="R31" t="n">
-        <v>6806664</v>
+        <v>6806619</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3730,6 +3758,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3747,13 +3776,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215873</t>
+          <t>https://artportalen.se/Sighting/129215872</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129215874</v>
+        <v>129215873</v>
       </c>
       <c r="B32" t="n">
         <v>79327</v>
@@ -3788,10 +3817,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>434483</v>
+        <v>434463</v>
       </c>
       <c r="R32" t="n">
-        <v>6806662</v>
+        <v>6806664</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3849,13 +3878,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215874</t>
+          <t>https://artportalen.se/Sighting/129215873</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129215875</v>
+        <v>129215874</v>
       </c>
       <c r="B33" t="n">
         <v>79327</v>
@@ -3890,10 +3919,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>434516</v>
+        <v>434483</v>
       </c>
       <c r="R33" t="n">
-        <v>6806695</v>
+        <v>6806662</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3951,13 +3980,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215875</t>
+          <t>https://artportalen.se/Sighting/129215874</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129215876</v>
+        <v>129215875</v>
       </c>
       <c r="B34" t="n">
         <v>79327</v>
@@ -3992,10 +4021,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>434591</v>
+        <v>434516</v>
       </c>
       <c r="R34" t="n">
-        <v>6806739</v>
+        <v>6806695</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4053,13 +4082,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215876</t>
+          <t>https://artportalen.se/Sighting/129215875</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129215877</v>
+        <v>129215876</v>
       </c>
       <c r="B35" t="n">
         <v>79327</v>
@@ -4094,10 +4123,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>434596</v>
+        <v>434591</v>
       </c>
       <c r="R35" t="n">
-        <v>6806729</v>
+        <v>6806739</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4155,13 +4184,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215877</t>
+          <t>https://artportalen.se/Sighting/129215876</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129215878</v>
+        <v>129215877</v>
       </c>
       <c r="B36" t="n">
         <v>79327</v>
@@ -4190,19 +4219,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>434621</v>
+        <v>434596</v>
       </c>
       <c r="R36" t="n">
-        <v>6806786</v>
+        <v>6806729</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4243,7 +4269,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4261,13 +4286,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215878</t>
+          <t>https://artportalen.se/Sighting/129215877</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129215879</v>
+        <v>129215878</v>
       </c>
       <c r="B37" t="n">
         <v>79327</v>
@@ -4296,16 +4321,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>434627</v>
+        <v>434621</v>
       </c>
       <c r="R37" t="n">
-        <v>6806787</v>
+        <v>6806786</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4346,6 +4374,7 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4363,13 +4392,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215879</t>
+          <t>https://artportalen.se/Sighting/129215878</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129215880</v>
+        <v>129215879</v>
       </c>
       <c r="B38" t="n">
         <v>79327</v>
@@ -4404,10 +4433,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>434845</v>
+        <v>434627</v>
       </c>
       <c r="R38" t="n">
-        <v>6806812</v>
+        <v>6806787</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4465,13 +4494,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215880</t>
+          <t>https://artportalen.se/Sighting/129215879</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129215881</v>
+        <v>129215880</v>
       </c>
       <c r="B39" t="n">
         <v>79327</v>
@@ -4500,19 +4529,16 @@
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>434834</v>
+        <v>434845</v>
       </c>
       <c r="R39" t="n">
-        <v>6806837</v>
+        <v>6806812</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,7 +4579,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -4571,13 +4596,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215881</t>
+          <t>https://artportalen.se/Sighting/129215880</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129215882</v>
+        <v>129215881</v>
       </c>
       <c r="B40" t="n">
         <v>79327</v>
@@ -4606,16 +4631,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>434851</v>
+        <v>434834</v>
       </c>
       <c r="R40" t="n">
-        <v>6806867</v>
+        <v>6806837</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4656,6 +4684,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -4673,13 +4702,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215882</t>
+          <t>https://artportalen.se/Sighting/129215881</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129215883</v>
+        <v>129215882</v>
       </c>
       <c r="B41" t="n">
         <v>79327</v>
@@ -4708,19 +4737,16 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>434920</v>
+        <v>434851</v>
       </c>
       <c r="R41" t="n">
-        <v>6806876</v>
+        <v>6806867</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4755,18 +4781,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4784,13 +4804,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215883</t>
+          <t>https://artportalen.se/Sighting/129215882</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129215884</v>
+        <v>129215883</v>
       </c>
       <c r="B42" t="n">
         <v>79327</v>
@@ -4819,16 +4839,19 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>434890</v>
+        <v>434920</v>
       </c>
       <c r="R42" t="n">
-        <v>6806827</v>
+        <v>6806876</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4863,12 +4886,18 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -4886,13 +4915,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215884</t>
+          <t>https://artportalen.se/Sighting/129215883</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129215885</v>
+        <v>129215884</v>
       </c>
       <c r="B43" t="n">
         <v>79327</v>
@@ -4927,10 +4956,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>434884</v>
+        <v>434890</v>
       </c>
       <c r="R43" t="n">
-        <v>6806816</v>
+        <v>6806827</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,13 +5017,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215885</t>
+          <t>https://artportalen.se/Sighting/129215884</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129215886</v>
+        <v>129215885</v>
       </c>
       <c r="B44" t="n">
         <v>79327</v>
@@ -5029,10 +5058,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>434934</v>
+        <v>434884</v>
       </c>
       <c r="R44" t="n">
-        <v>6806762</v>
+        <v>6806816</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5090,13 +5119,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215886</t>
+          <t>https://artportalen.se/Sighting/129215885</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129215887</v>
+        <v>129215886</v>
       </c>
       <c r="B45" t="n">
         <v>79327</v>
@@ -5131,10 +5160,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>434936</v>
+        <v>434934</v>
       </c>
       <c r="R45" t="n">
-        <v>6806726</v>
+        <v>6806762</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5192,13 +5221,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215887</t>
+          <t>https://artportalen.se/Sighting/129215886</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129215888</v>
+        <v>129215887</v>
       </c>
       <c r="B46" t="n">
         <v>79327</v>
@@ -5233,10 +5262,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>434913</v>
+        <v>434936</v>
       </c>
       <c r="R46" t="n">
-        <v>6806699</v>
+        <v>6806726</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5294,13 +5323,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215888</t>
+          <t>https://artportalen.se/Sighting/129215887</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129215889</v>
+        <v>129215888</v>
       </c>
       <c r="B47" t="n">
         <v>79327</v>
@@ -5335,10 +5364,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>434813</v>
+        <v>434913</v>
       </c>
       <c r="R47" t="n">
-        <v>6806692</v>
+        <v>6806699</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5396,13 +5425,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215889</t>
+          <t>https://artportalen.se/Sighting/129215888</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129215890</v>
+        <v>129215889</v>
       </c>
       <c r="B48" t="n">
         <v>79327</v>
@@ -5437,10 +5466,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>434799</v>
+        <v>434813</v>
       </c>
       <c r="R48" t="n">
-        <v>6806670</v>
+        <v>6806692</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5498,13 +5527,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215890</t>
+          <t>https://artportalen.se/Sighting/129215889</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129215891</v>
+        <v>129215890</v>
       </c>
       <c r="B49" t="n">
         <v>79327</v>
@@ -5539,10 +5568,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>434812</v>
+        <v>434799</v>
       </c>
       <c r="R49" t="n">
-        <v>6806610</v>
+        <v>6806670</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5600,13 +5629,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215891</t>
+          <t>https://artportalen.se/Sighting/129215890</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129215892</v>
+        <v>129215891</v>
       </c>
       <c r="B50" t="n">
         <v>79327</v>
@@ -5641,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>434884</v>
+        <v>434812</v>
       </c>
       <c r="R50" t="n">
-        <v>6806606</v>
+        <v>6806610</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5702,13 +5731,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215892</t>
+          <t>https://artportalen.se/Sighting/129215891</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129215893</v>
+        <v>129215892</v>
       </c>
       <c r="B51" t="n">
         <v>79327</v>
@@ -5743,10 +5772,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>434908</v>
+        <v>434884</v>
       </c>
       <c r="R51" t="n">
-        <v>6806633</v>
+        <v>6806606</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5804,13 +5833,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215893</t>
+          <t>https://artportalen.se/Sighting/129215892</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129215895</v>
+        <v>129215893</v>
       </c>
       <c r="B52" t="n">
         <v>79327</v>
@@ -5845,10 +5874,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>434858</v>
+        <v>434908</v>
       </c>
       <c r="R52" t="n">
-        <v>6806562</v>
+        <v>6806633</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5906,13 +5935,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215895</t>
+          <t>https://artportalen.se/Sighting/129215893</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129215896</v>
+        <v>129215895</v>
       </c>
       <c r="B53" t="n">
         <v>79327</v>
@@ -5947,10 +5976,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>434783</v>
+        <v>434858</v>
       </c>
       <c r="R53" t="n">
-        <v>6806478</v>
+        <v>6806562</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6008,13 +6037,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215896</t>
+          <t>https://artportalen.se/Sighting/129215895</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129215898</v>
+        <v>129215896</v>
       </c>
       <c r="B54" t="n">
         <v>79327</v>
@@ -6049,10 +6078,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>434759</v>
+        <v>434783</v>
       </c>
       <c r="R54" t="n">
-        <v>6806455</v>
+        <v>6806478</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6110,13 +6139,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215898</t>
+          <t>https://artportalen.se/Sighting/129215896</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129215899</v>
+        <v>129215898</v>
       </c>
       <c r="B55" t="n">
         <v>79327</v>
@@ -6151,10 +6180,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>434763</v>
+        <v>434759</v>
       </c>
       <c r="R55" t="n">
-        <v>6806436</v>
+        <v>6806455</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6212,13 +6241,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215899</t>
+          <t>https://artportalen.se/Sighting/129215898</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129215900</v>
+        <v>129215899</v>
       </c>
       <c r="B56" t="n">
         <v>79327</v>
@@ -6253,10 +6282,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>434775</v>
+        <v>434763</v>
       </c>
       <c r="R56" t="n">
-        <v>6806423</v>
+        <v>6806436</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6314,13 +6343,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215900</t>
+          <t>https://artportalen.se/Sighting/129215899</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129215901</v>
+        <v>129215900</v>
       </c>
       <c r="B57" t="n">
         <v>79327</v>
@@ -6355,10 +6384,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>434918</v>
+        <v>434775</v>
       </c>
       <c r="R57" t="n">
-        <v>6806737</v>
+        <v>6806423</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6416,13 +6445,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215901</t>
+          <t>https://artportalen.se/Sighting/129215900</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129215902</v>
+        <v>129215901</v>
       </c>
       <c r="B58" t="n">
         <v>79327</v>
@@ -6451,19 +6480,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>434784</v>
+        <v>434918</v>
       </c>
       <c r="R58" t="n">
-        <v>6806543</v>
+        <v>6806737</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6498,18 +6524,12 @@
           <t>2025-10-19</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
       </c>
@@ -6527,38 +6547,38 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215902</t>
+          <t>https://artportalen.se/Sighting/129215901</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129215819</v>
+        <v>129215902</v>
       </c>
       <c r="B59" t="n">
-        <v>79084</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6571,10 +6591,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>434773</v>
+        <v>434784</v>
       </c>
       <c r="R59" t="n">
-        <v>6806803</v>
+        <v>6806543</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6609,6 +6629,11 @@
           <t>2025-10-19</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6633,54 +6658,54 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215819</t>
+          <t>https://artportalen.se/Sighting/129215902</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129215821</v>
+        <v>137044151</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>79480</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>434913</v>
+        <v>434241</v>
       </c>
       <c r="R60" t="n">
-        <v>6806785</v>
+        <v>6806634</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6704,12 +6729,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:43</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6729,60 +6764,60 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Göran Rönning, Elisa Andersson, Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215821</t>
+          <t>https://artportalen.se/Sighting/137044151</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129215822</v>
+        <v>137044159</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>79480</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>434936</v>
+        <v>434134</v>
       </c>
       <c r="R61" t="n">
-        <v>6806756</v>
+        <v>6806558</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6806,12 +6841,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6831,60 +6876,60 @@
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Göran Rönning, Elisa Andersson, Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215822</t>
+          <t>https://artportalen.se/Sighting/137044159</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129215823</v>
+        <v>137044522</v>
       </c>
       <c r="B62" t="n">
-        <v>79084</v>
+        <v>79480</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>434906</v>
+        <v>434412</v>
       </c>
       <c r="R62" t="n">
-        <v>6806734</v>
+        <v>6806523</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6908,12 +6953,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6924,69 +6979,79 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215823</t>
+          <t>https://artportalen.se/Sighting/137044522</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129215824</v>
+        <v>137044523</v>
       </c>
       <c r="B63" t="n">
-        <v>79084</v>
+        <v>79480</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>434922</v>
+        <v>434438</v>
       </c>
       <c r="R63" t="n">
-        <v>6806746</v>
+        <v>6806526</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7010,12 +7075,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7026,69 +7101,79 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215824</t>
+          <t>https://artportalen.se/Sighting/137044523</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129215825</v>
+        <v>137044524</v>
       </c>
       <c r="B64" t="n">
-        <v>79084</v>
+        <v>79480</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>434799</v>
+        <v>434480</v>
       </c>
       <c r="R64" t="n">
-        <v>6806687</v>
+        <v>6806482</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7112,12 +7197,22 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7128,69 +7223,79 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Död gren</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Dead branch</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215825</t>
+          <t>https://artportalen.se/Sighting/137044524</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129215734</v>
+        <v>137044527</v>
       </c>
       <c r="B65" t="n">
-        <v>79946</v>
+        <v>79480</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>434546</v>
+        <v>434659</v>
       </c>
       <c r="R65" t="n">
-        <v>6806737</v>
+        <v>6806504</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7214,12 +7319,22 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>14:30</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7230,31 +7345,41 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215734</t>
+          <t>https://artportalen.se/Sighting/137044527</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129215735</v>
+        <v>129215819</v>
       </c>
       <c r="B66" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7262,34 +7387,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>434571</v>
+        <v>434773</v>
       </c>
       <c r="R66" t="n">
-        <v>6806718</v>
+        <v>6806803</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7330,6 +7458,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7347,16 +7476,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215735</t>
+          <t>https://artportalen.se/Sighting/129215819</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129215736</v>
+        <v>129215821</v>
       </c>
       <c r="B67" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7364,21 +7493,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7388,10 +7517,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>434605</v>
+        <v>434913</v>
       </c>
       <c r="R67" t="n">
-        <v>6806750</v>
+        <v>6806785</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7449,16 +7578,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215736</t>
+          <t>https://artportalen.se/Sighting/129215821</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129215737</v>
+        <v>129215822</v>
       </c>
       <c r="B68" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7466,21 +7595,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7490,10 +7619,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>434585</v>
+        <v>434936</v>
       </c>
       <c r="R68" t="n">
-        <v>6806746</v>
+        <v>6806756</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7551,16 +7680,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215737</t>
+          <t>https://artportalen.se/Sighting/129215822</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129215738</v>
+        <v>129215823</v>
       </c>
       <c r="B69" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7568,21 +7697,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7592,10 +7721,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>434764</v>
+        <v>434906</v>
       </c>
       <c r="R69" t="n">
-        <v>6806804</v>
+        <v>6806734</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7653,16 +7782,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215738</t>
+          <t>https://artportalen.se/Sighting/129215823</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129215739</v>
+        <v>129215824</v>
       </c>
       <c r="B70" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7670,21 +7799,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7694,10 +7823,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>434817</v>
+        <v>434922</v>
       </c>
       <c r="R70" t="n">
-        <v>6806766</v>
+        <v>6806746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7755,16 +7884,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215739</t>
+          <t>https://artportalen.se/Sighting/129215824</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129215741</v>
+        <v>129215825</v>
       </c>
       <c r="B71" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7772,21 +7901,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7796,10 +7925,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>434844</v>
+        <v>434799</v>
       </c>
       <c r="R71" t="n">
-        <v>6806852</v>
+        <v>6806687</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7857,13 +7986,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215741</t>
+          <t>https://artportalen.se/Sighting/129215825</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129215742</v>
+        <v>129215734</v>
       </c>
       <c r="B72" t="n">
         <v>79946</v>
@@ -7892,19 +8021,16 @@
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>434910</v>
+        <v>434546</v>
       </c>
       <c r="R72" t="n">
-        <v>6806856</v>
+        <v>6806737</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7945,7 +8071,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7963,13 +8088,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215742</t>
+          <t>https://artportalen.se/Sighting/129215734</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129215743</v>
+        <v>129215735</v>
       </c>
       <c r="B73" t="n">
         <v>79946</v>
@@ -8004,10 +8129,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>434922</v>
+        <v>434571</v>
       </c>
       <c r="R73" t="n">
-        <v>6806795</v>
+        <v>6806718</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8065,13 +8190,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215743</t>
+          <t>https://artportalen.se/Sighting/129215735</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129215744</v>
+        <v>129215736</v>
       </c>
       <c r="B74" t="n">
         <v>79946</v>
@@ -8100,19 +8225,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>434950</v>
+        <v>434605</v>
       </c>
       <c r="R74" t="n">
-        <v>6806749</v>
+        <v>6806750</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8153,7 +8275,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8171,13 +8292,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215744</t>
+          <t>https://artportalen.se/Sighting/129215736</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129215745</v>
+        <v>129215737</v>
       </c>
       <c r="B75" t="n">
         <v>79946</v>
@@ -8212,10 +8333,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>434934</v>
+        <v>434585</v>
       </c>
       <c r="R75" t="n">
-        <v>6806753</v>
+        <v>6806746</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8273,13 +8394,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215745</t>
+          <t>https://artportalen.se/Sighting/129215737</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129215749</v>
+        <v>129215738</v>
       </c>
       <c r="B76" t="n">
         <v>79946</v>
@@ -8314,10 +8435,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>434932</v>
+        <v>434764</v>
       </c>
       <c r="R76" t="n">
-        <v>6806615</v>
+        <v>6806804</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8375,13 +8496,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215749</t>
+          <t>https://artportalen.se/Sighting/129215738</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129215750</v>
+        <v>129215739</v>
       </c>
       <c r="B77" t="n">
         <v>79946</v>
@@ -8416,10 +8537,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>434775</v>
+        <v>434817</v>
       </c>
       <c r="R77" t="n">
-        <v>6806482</v>
+        <v>6806766</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8477,13 +8598,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215750</t>
+          <t>https://artportalen.se/Sighting/129215739</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129215904</v>
+        <v>129215741</v>
       </c>
       <c r="B78" t="n">
         <v>79946</v>
@@ -8518,10 +8639,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>434857</v>
+        <v>434844</v>
       </c>
       <c r="R78" t="n">
-        <v>6806833</v>
+        <v>6806852</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8579,48 +8700,43 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215904</t>
+          <t>https://artportalen.se/Sighting/129215741</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129215795</v>
+        <v>129215742</v>
       </c>
       <c r="B79" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8628,10 +8744,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>434758</v>
+        <v>434910</v>
       </c>
       <c r="R79" t="n">
-        <v>6806435</v>
+        <v>6806856</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8672,6 +8788,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8689,59 +8806,51 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215795</t>
+          <t>https://artportalen.se/Sighting/129215742</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129215796</v>
+        <v>129215743</v>
       </c>
       <c r="B80" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>434635</v>
+        <v>434922</v>
       </c>
       <c r="R80" t="n">
-        <v>6806453</v>
+        <v>6806795</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8799,48 +8908,43 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215796</t>
+          <t>https://artportalen.se/Sighting/129215743</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129215797</v>
+        <v>129215744</v>
       </c>
       <c r="B81" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8848,10 +8952,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>434602</v>
+        <v>434950</v>
       </c>
       <c r="R81" t="n">
-        <v>6806495</v>
+        <v>6806749</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8892,6 +8996,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8909,59 +9014,51 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215797</t>
+          <t>https://artportalen.se/Sighting/129215744</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129215798</v>
+        <v>129215745</v>
       </c>
       <c r="B82" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>434244</v>
+        <v>434934</v>
       </c>
       <c r="R82" t="n">
-        <v>6806571</v>
+        <v>6806753</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9019,59 +9116,51 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215798</t>
+          <t>https://artportalen.se/Sighting/129215745</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129215799</v>
+        <v>129215749</v>
       </c>
       <c r="B83" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>434142</v>
+        <v>434932</v>
       </c>
       <c r="R83" t="n">
-        <v>6806549</v>
+        <v>6806615</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9129,59 +9218,51 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215799</t>
+          <t>https://artportalen.se/Sighting/129215749</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129215800</v>
+        <v>129215750</v>
       </c>
       <c r="B84" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>434596</v>
+        <v>434775</v>
       </c>
       <c r="R84" t="n">
-        <v>6806728</v>
+        <v>6806482</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9239,59 +9320,51 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215800</t>
+          <t>https://artportalen.se/Sighting/129215750</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129215801</v>
+        <v>129215904</v>
       </c>
       <c r="B85" t="n">
-        <v>57950</v>
+        <v>79946</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>434883</v>
+        <v>434857</v>
       </c>
       <c r="R85" t="n">
-        <v>6806894</v>
+        <v>6806833</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9349,13 +9422,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215801</t>
+          <t>https://artportalen.se/Sighting/129215904</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129215802</v>
+        <v>129215795</v>
       </c>
       <c r="B86" t="n">
         <v>57950</v>
@@ -9398,10 +9471,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>434910</v>
+        <v>434758</v>
       </c>
       <c r="R86" t="n">
-        <v>6806898</v>
+        <v>6806435</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9459,13 +9532,13 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215802</t>
+          <t>https://artportalen.se/Sighting/129215795</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129215803</v>
+        <v>129215796</v>
       </c>
       <c r="B87" t="n">
         <v>57950</v>
@@ -9508,10 +9581,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>434895</v>
+        <v>434635</v>
       </c>
       <c r="R87" t="n">
-        <v>6806664</v>
+        <v>6806453</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9569,13 +9642,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215803</t>
+          <t>https://artportalen.se/Sighting/129215796</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129215804</v>
+        <v>129215797</v>
       </c>
       <c r="B88" t="n">
         <v>57950</v>
@@ -9618,10 +9691,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>434880</v>
+        <v>434602</v>
       </c>
       <c r="R88" t="n">
-        <v>6806584</v>
+        <v>6806495</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9679,13 +9752,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215804</t>
+          <t>https://artportalen.se/Sighting/129215797</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129215805</v>
+        <v>129215798</v>
       </c>
       <c r="B89" t="n">
         <v>57950</v>
@@ -9718,7 +9791,7 @@
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
@@ -9728,10 +9801,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>434761</v>
+        <v>434244</v>
       </c>
       <c r="R89" t="n">
-        <v>6806449</v>
+        <v>6806571</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9789,16 +9862,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215805</t>
+          <t>https://artportalen.se/Sighting/129215798</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129215764</v>
+        <v>129215799</v>
       </c>
       <c r="B90" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9806,21 +9879,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9828,7 +9901,7 @@
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
@@ -9838,10 +9911,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>434687</v>
+        <v>434142</v>
       </c>
       <c r="R90" t="n">
-        <v>6806459</v>
+        <v>6806549</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9899,16 +9972,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215764</t>
+          <t>https://artportalen.se/Sighting/129215799</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129215765</v>
+        <v>129215800</v>
       </c>
       <c r="B91" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9916,21 +9989,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9938,7 +10011,7 @@
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
@@ -9948,10 +10021,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>434630</v>
+        <v>434596</v>
       </c>
       <c r="R91" t="n">
-        <v>6806465</v>
+        <v>6806728</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10009,16 +10082,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215765</t>
+          <t>https://artportalen.se/Sighting/129215800</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129215766</v>
+        <v>129215801</v>
       </c>
       <c r="B92" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10026,21 +10099,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10048,7 +10121,7 @@
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
@@ -10058,10 +10131,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>434601</v>
+        <v>434883</v>
       </c>
       <c r="R92" t="n">
-        <v>6806475</v>
+        <v>6806894</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10119,16 +10192,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215766</t>
+          <t>https://artportalen.se/Sighting/129215801</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129215767</v>
+        <v>129215802</v>
       </c>
       <c r="B93" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10136,21 +10209,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10158,7 +10231,7 @@
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
@@ -10168,10 +10241,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>434546</v>
+        <v>434910</v>
       </c>
       <c r="R93" t="n">
-        <v>6806482</v>
+        <v>6806898</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10229,16 +10302,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215767</t>
+          <t>https://artportalen.se/Sighting/129215802</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129215768</v>
+        <v>129215803</v>
       </c>
       <c r="B94" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10246,21 +10319,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10268,7 +10341,7 @@
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
@@ -10278,10 +10351,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>434422</v>
+        <v>434895</v>
       </c>
       <c r="R94" t="n">
-        <v>6806522</v>
+        <v>6806664</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10339,16 +10412,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215768</t>
+          <t>https://artportalen.se/Sighting/129215803</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129215769</v>
+        <v>129215804</v>
       </c>
       <c r="B95" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10356,21 +10429,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10378,7 +10451,7 @@
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
@@ -10388,10 +10461,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>434382</v>
+        <v>434880</v>
       </c>
       <c r="R95" t="n">
-        <v>6806548</v>
+        <v>6806584</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10449,16 +10522,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215769</t>
+          <t>https://artportalen.se/Sighting/129215804</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129215770</v>
+        <v>129215805</v>
       </c>
       <c r="B96" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10466,21 +10539,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10488,7 +10561,7 @@
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
@@ -10498,10 +10571,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>434136</v>
+        <v>434761</v>
       </c>
       <c r="R96" t="n">
-        <v>6806558</v>
+        <v>6806449</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10559,13 +10632,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215770</t>
+          <t>https://artportalen.se/Sighting/129215805</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129215771</v>
+        <v>129215764</v>
       </c>
       <c r="B97" t="n">
         <v>57141</v>
@@ -10608,10 +10681,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>434229</v>
+        <v>434687</v>
       </c>
       <c r="R97" t="n">
-        <v>6806613</v>
+        <v>6806459</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10669,13 +10742,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215771</t>
+          <t>https://artportalen.se/Sighting/129215764</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129215772</v>
+        <v>129215765</v>
       </c>
       <c r="B98" t="n">
         <v>57141</v>
@@ -10718,10 +10791,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>434228</v>
+        <v>434630</v>
       </c>
       <c r="R98" t="n">
-        <v>6806632</v>
+        <v>6806465</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10779,13 +10852,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215772</t>
+          <t>https://artportalen.se/Sighting/129215765</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129215773</v>
+        <v>129215766</v>
       </c>
       <c r="B99" t="n">
         <v>57141</v>
@@ -10828,10 +10901,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>434241</v>
+        <v>434601</v>
       </c>
       <c r="R99" t="n">
-        <v>6806606</v>
+        <v>6806475</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10889,13 +10962,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215773</t>
+          <t>https://artportalen.se/Sighting/129215766</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129215774</v>
+        <v>129215767</v>
       </c>
       <c r="B100" t="n">
         <v>57141</v>
@@ -10938,10 +11011,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>434307</v>
+        <v>434546</v>
       </c>
       <c r="R100" t="n">
-        <v>6806608</v>
+        <v>6806482</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10999,13 +11072,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215774</t>
+          <t>https://artportalen.se/Sighting/129215767</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129215775</v>
+        <v>129215768</v>
       </c>
       <c r="B101" t="n">
         <v>57141</v>
@@ -11048,10 +11121,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>434334</v>
+        <v>434422</v>
       </c>
       <c r="R101" t="n">
-        <v>6806593</v>
+        <v>6806522</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11109,13 +11182,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215775</t>
+          <t>https://artportalen.se/Sighting/129215768</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129215776</v>
+        <v>129215769</v>
       </c>
       <c r="B102" t="n">
         <v>57141</v>
@@ -11158,10 +11231,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>434445</v>
+        <v>434382</v>
       </c>
       <c r="R102" t="n">
-        <v>6806699</v>
+        <v>6806548</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11219,13 +11292,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215776</t>
+          <t>https://artportalen.se/Sighting/129215769</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129215777</v>
+        <v>129215770</v>
       </c>
       <c r="B103" t="n">
         <v>57141</v>
@@ -11258,7 +11331,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11268,10 +11341,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>434432</v>
+        <v>434136</v>
       </c>
       <c r="R103" t="n">
-        <v>6806670</v>
+        <v>6806558</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11329,13 +11402,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215777</t>
+          <t>https://artportalen.se/Sighting/129215770</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129215779</v>
+        <v>129215771</v>
       </c>
       <c r="B104" t="n">
         <v>57141</v>
@@ -11378,10 +11451,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>434440</v>
+        <v>434229</v>
       </c>
       <c r="R104" t="n">
-        <v>6806641</v>
+        <v>6806613</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11439,13 +11512,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215779</t>
+          <t>https://artportalen.se/Sighting/129215771</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129215780</v>
+        <v>129215772</v>
       </c>
       <c r="B105" t="n">
         <v>57141</v>
@@ -11488,10 +11561,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>434449</v>
+        <v>434228</v>
       </c>
       <c r="R105" t="n">
-        <v>6806667</v>
+        <v>6806632</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11549,13 +11622,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215780</t>
+          <t>https://artportalen.se/Sighting/129215772</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129215781</v>
+        <v>129215773</v>
       </c>
       <c r="B106" t="n">
         <v>57141</v>
@@ -11598,10 +11671,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>434481</v>
+        <v>434241</v>
       </c>
       <c r="R106" t="n">
-        <v>6806660</v>
+        <v>6806606</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11659,13 +11732,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215781</t>
+          <t>https://artportalen.se/Sighting/129215773</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129215782</v>
+        <v>129215774</v>
       </c>
       <c r="B107" t="n">
         <v>57141</v>
@@ -11708,10 +11781,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>434568</v>
+        <v>434307</v>
       </c>
       <c r="R107" t="n">
-        <v>6806730</v>
+        <v>6806608</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11769,13 +11842,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215782</t>
+          <t>https://artportalen.se/Sighting/129215774</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129215783</v>
+        <v>129215775</v>
       </c>
       <c r="B108" t="n">
         <v>57141</v>
@@ -11818,10 +11891,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>434919</v>
+        <v>434334</v>
       </c>
       <c r="R108" t="n">
-        <v>6806862</v>
+        <v>6806593</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11879,13 +11952,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215783</t>
+          <t>https://artportalen.se/Sighting/129215775</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129215784</v>
+        <v>129215776</v>
       </c>
       <c r="B109" t="n">
         <v>57141</v>
@@ -11928,10 +12001,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>434853</v>
+        <v>434445</v>
       </c>
       <c r="R109" t="n">
-        <v>6806697</v>
+        <v>6806699</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11989,13 +12062,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215784</t>
+          <t>https://artportalen.se/Sighting/129215776</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129215785</v>
+        <v>129215777</v>
       </c>
       <c r="B110" t="n">
         <v>57141</v>
@@ -12028,7 +12101,7 @@
       <c r="L110" t="inlineStr"/>
       <c r="M110" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
@@ -12038,10 +12111,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>434945</v>
+        <v>434432</v>
       </c>
       <c r="R110" t="n">
-        <v>6806613</v>
+        <v>6806670</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12099,13 +12172,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215785</t>
+          <t>https://artportalen.se/Sighting/129215777</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129215786</v>
+        <v>129215779</v>
       </c>
       <c r="B111" t="n">
         <v>57141</v>
@@ -12148,10 +12221,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>434883</v>
+        <v>434440</v>
       </c>
       <c r="R111" t="n">
-        <v>6806675</v>
+        <v>6806641</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12209,13 +12282,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215786</t>
+          <t>https://artportalen.se/Sighting/129215779</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129215787</v>
+        <v>129215780</v>
       </c>
       <c r="B112" t="n">
         <v>57141</v>
@@ -12258,10 +12331,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>434813</v>
+        <v>434449</v>
       </c>
       <c r="R112" t="n">
-        <v>6806656</v>
+        <v>6806667</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12319,13 +12392,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215787</t>
+          <t>https://artportalen.se/Sighting/129215780</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129215790</v>
+        <v>129215781</v>
       </c>
       <c r="B113" t="n">
         <v>57141</v>
@@ -12368,10 +12441,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>434809</v>
+        <v>434481</v>
       </c>
       <c r="R113" t="n">
-        <v>6806535</v>
+        <v>6806660</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12429,16 +12502,16 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215790</t>
+          <t>https://artportalen.se/Sighting/129215781</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129215818</v>
+        <v>129215782</v>
       </c>
       <c r="B114" t="n">
-        <v>58327</v>
+        <v>57141</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12446,21 +12519,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12468,7 +12541,7 @@
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
@@ -12478,10 +12551,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>434849</v>
+        <v>434568</v>
       </c>
       <c r="R114" t="n">
-        <v>6806700</v>
+        <v>6806730</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12539,38 +12612,38 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215818</t>
+          <t>https://artportalen.se/Sighting/129215782</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129215793</v>
+        <v>129215783</v>
       </c>
       <c r="B115" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12578,7 +12651,7 @@
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
@@ -12588,10 +12661,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>434920</v>
+        <v>434919</v>
       </c>
       <c r="R115" t="n">
-        <v>6806792</v>
+        <v>6806862</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12649,38 +12722,38 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215793</t>
+          <t>https://artportalen.se/Sighting/129215783</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129215794</v>
+        <v>129215784</v>
       </c>
       <c r="B116" t="n">
-        <v>58114</v>
+        <v>57141</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12688,7 +12761,7 @@
       <c r="L116" t="inlineStr"/>
       <c r="M116" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
@@ -12698,10 +12771,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>434852</v>
+        <v>434853</v>
       </c>
       <c r="R116" t="n">
-        <v>6806551</v>
+        <v>6806697</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12759,16 +12832,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215794</t>
+          <t>https://artportalen.se/Sighting/129215784</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129215807</v>
+        <v>129215785</v>
       </c>
       <c r="B117" t="n">
-        <v>97989</v>
+        <v>57141</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12776,27 +12849,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -12804,10 +12881,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>434541</v>
+        <v>434945</v>
       </c>
       <c r="R117" t="n">
-        <v>6806479</v>
+        <v>6806613</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12848,7 +12925,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12866,51 +12942,59 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215807</t>
+          <t>https://artportalen.se/Sighting/129215785</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129215808</v>
+        <v>129215786</v>
       </c>
       <c r="B118" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>434355</v>
+        <v>434883</v>
       </c>
       <c r="R118" t="n">
-        <v>6806519</v>
+        <v>6806675</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12968,51 +13052,59 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215808</t>
+          <t>https://artportalen.se/Sighting/129215786</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129215809</v>
+        <v>129215787</v>
       </c>
       <c r="B119" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>434843</v>
+        <v>434813</v>
       </c>
       <c r="R119" t="n">
-        <v>6806853</v>
+        <v>6806656</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13070,51 +13162,59 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215809</t>
+          <t>https://artportalen.se/Sighting/129215787</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129215810</v>
+        <v>129215790</v>
       </c>
       <c r="B120" t="n">
-        <v>79085</v>
+        <v>57141</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Borgbliket, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>434908</v>
+        <v>434809</v>
       </c>
       <c r="R120" t="n">
-        <v>6806733</v>
+        <v>6806535</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13172,54 +13272,59 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215810</t>
+          <t>https://artportalen.se/Sighting/129215790</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129215812</v>
+        <v>137044152</v>
       </c>
       <c r="B121" t="n">
-        <v>79085</v>
+        <v>57195</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>434922</v>
+        <v>434204</v>
       </c>
       <c r="R121" t="n">
-        <v>6806746</v>
+        <v>6806571</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13243,12 +13348,27 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>10:46</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>10:46</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Tjäderbetad tall.</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13268,60 +13388,65 @@
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Göran Rönning, Elisa Andersson, Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215812</t>
+          <t>https://artportalen.se/Sighting/137044152</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129215813</v>
+        <v>137044153</v>
       </c>
       <c r="B122" t="n">
-        <v>79085</v>
+        <v>57195</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>434803</v>
+        <v>434194</v>
       </c>
       <c r="R122" t="n">
-        <v>6806683</v>
+        <v>6806545</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13345,12 +13470,27 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>10:53</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>10:53</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Tjäderbetade tallar, 2 st</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13370,57 +13510,62 @@
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Göran Rönning, Elisa Andersson, Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215813</t>
+          <t>https://artportalen.se/Sighting/137044153</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129215751</v>
+        <v>137044154</v>
       </c>
       <c r="B123" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>434673</v>
+        <v>434150</v>
       </c>
       <c r="R123" t="n">
-        <v>6806460</v>
+        <v>6806554</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13447,12 +13592,22 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13472,60 +13627,65 @@
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Göran Rönning, Elisa Andersson, Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215751</t>
+          <t>https://artportalen.se/Sighting/137044154</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129215752</v>
+        <v>137044158</v>
       </c>
       <c r="B124" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>434263</v>
+        <v>434135</v>
       </c>
       <c r="R124" t="n">
-        <v>6806561</v>
+        <v>6806557</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13549,12 +13709,22 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13574,60 +13744,65 @@
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Göran Rönning, Elisa Andersson, Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215752</t>
+          <t>https://artportalen.se/Sighting/137044158</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129215753</v>
+        <v>137044160</v>
       </c>
       <c r="B125" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>434571</v>
+        <v>434261</v>
       </c>
       <c r="R125" t="n">
-        <v>6806718</v>
+        <v>6806573</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13651,12 +13826,27 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:27</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Tjäderbetade tallar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13676,60 +13866,65 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Göran Rönning, Elisa Andersson, Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215753</t>
+          <t>https://artportalen.se/Sighting/137044160</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129215754</v>
+        <v>137044161</v>
       </c>
       <c r="B126" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>434774</v>
+        <v>434277</v>
       </c>
       <c r="R126" t="n">
-        <v>6806803</v>
+        <v>6806573</v>
       </c>
       <c r="S126" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T126" t="inlineStr">
         <is>
@@ -13753,12 +13948,27 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Tjäderbetad tall och färsk spillning efter tjädertupp.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13778,60 +13988,68 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Eva Löfqvist, Göran Rönning, Elisa Andersson, Evalena Sköld, Åke Sköld</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215754</t>
+          <t>https://artportalen.se/Sighting/137044161</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129215755</v>
+        <v>137044506</v>
       </c>
       <c r="B127" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>434812</v>
+        <v>434205</v>
       </c>
       <c r="R127" t="n">
-        <v>6806771</v>
+        <v>6806563</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13855,12 +14073,27 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:52</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr">
+        <is>
+          <t>Fjäder från tjädertupp</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13875,68 +14108,73 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215755</t>
+          <t>https://artportalen.se/Sighting/137044506</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129215756</v>
+        <v>137044507</v>
       </c>
       <c r="B128" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
-      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>434857</v>
+        <v>434085</v>
       </c>
       <c r="R128" t="n">
-        <v>6806824</v>
+        <v>6806519</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13960,12 +14198,27 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Ett 10-tal tjäderbetade tallar inom synhåll</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -13974,72 +14227,79 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
-      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215756</t>
+          <t>https://artportalen.se/Sighting/137044507</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>129215757</v>
+        <v>137044508</v>
       </c>
       <c r="B129" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>434905</v>
+        <v>434055</v>
       </c>
       <c r="R129" t="n">
-        <v>6806832</v>
+        <v>6806537</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14063,12 +14323,22 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14083,65 +14353,70 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215757</t>
+          <t>https://artportalen.se/Sighting/137044508</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129215758</v>
+        <v>137044519</v>
       </c>
       <c r="B130" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>434928</v>
+        <v>434065</v>
       </c>
       <c r="R130" t="n">
-        <v>6806794</v>
+        <v>6806539</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14165,12 +14440,27 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Färsk spillning under tjäderbetad tall</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14185,65 +14475,70 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215758</t>
+          <t>https://artportalen.se/Sighting/137044519</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129215759</v>
+        <v>137044521</v>
       </c>
       <c r="B131" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>434930</v>
+        <v>434347</v>
       </c>
       <c r="R131" t="n">
-        <v>6806768</v>
+        <v>6806556</v>
       </c>
       <c r="S131" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14267,12 +14562,27 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Balgrop i myrstack, samt färsk spillning</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14287,65 +14597,70 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215759</t>
+          <t>https://artportalen.se/Sighting/137044521</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129215760</v>
+        <v>137044526</v>
       </c>
       <c r="B132" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>434895</v>
+        <v>434618</v>
       </c>
       <c r="R132" t="n">
-        <v>6806736</v>
+        <v>6806499</v>
       </c>
       <c r="S132" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14369,12 +14684,22 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>14:27</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14389,65 +14714,70 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215760</t>
+          <t>https://artportalen.se/Sighting/137044526</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129215761</v>
+        <v>137044528</v>
       </c>
       <c r="B133" t="n">
-        <v>79917</v>
+        <v>57195</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Borgbliket, Dlr</t>
+          <t>Borgblik, Dlr</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>434924</v>
+        <v>434671</v>
       </c>
       <c r="R133" t="n">
-        <v>6806749</v>
+        <v>6806502</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14471,12 +14801,27 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>14:32</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Tjäderbetad tall</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14491,16 +14836,2455 @@
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Eva Löfqvist</t>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044528</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>137044529</v>
+      </c>
+      <c r="B134" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Borgblik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>434692</v>
+      </c>
+      <c r="R134" t="n">
+        <v>6806575</v>
+      </c>
+      <c r="S134" t="n">
+        <v>5</v>
+      </c>
+      <c r="T134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U134" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>14:48</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Tjäderbetad tall</t>
+        </is>
+      </c>
+      <c r="AD134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="inlineStr"/>
+      <c r="AW134" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX134" t="inlineStr">
+        <is>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044529</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>137044530</v>
+      </c>
+      <c r="B135" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Borgblik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>434715</v>
+      </c>
+      <c r="R135" t="n">
+        <v>6806594</v>
+      </c>
+      <c r="S135" t="n">
+        <v>5</v>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U135" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Tjäderbetad tall</t>
+        </is>
+      </c>
+      <c r="AD135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="inlineStr"/>
+      <c r="AW135" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX135" t="inlineStr">
+        <is>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044530</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>137044531</v>
+      </c>
+      <c r="B136" t="n">
+        <v>57195</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Borgblik, Dlr</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>434760</v>
+      </c>
+      <c r="R136" t="n">
+        <v>6806677</v>
+      </c>
+      <c r="S136" t="n">
+        <v>7</v>
+      </c>
+      <c r="T136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U136" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>3 tjäderbetade tallar</t>
+        </is>
+      </c>
+      <c r="AD136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="inlineStr"/>
+      <c r="AW136" t="inlineStr">
+        <is>
+          <t>Elisa Andersson</t>
+        </is>
+      </c>
+      <c r="AX136" t="inlineStr">
+        <is>
+          <t>Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning, Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137044531</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>129215818</v>
+      </c>
+      <c r="B137" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr"/>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>434849</v>
+      </c>
+      <c r="R137" t="n">
+        <v>6806700</v>
+      </c>
+      <c r="S137" t="n">
+        <v>10</v>
+      </c>
+      <c r="T137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U137" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="inlineStr"/>
+      <c r="AW137" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX137" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215818</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>129215793</v>
+      </c>
+      <c r="B138" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr"/>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>434920</v>
+      </c>
+      <c r="R138" t="n">
+        <v>6806792</v>
+      </c>
+      <c r="S138" t="n">
+        <v>10</v>
+      </c>
+      <c r="T138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U138" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG138" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT138" t="inlineStr"/>
+      <c r="AW138" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX138" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215793</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>129215794</v>
+      </c>
+      <c r="B139" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr"/>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>434852</v>
+      </c>
+      <c r="R139" t="n">
+        <v>6806551</v>
+      </c>
+      <c r="S139" t="n">
+        <v>10</v>
+      </c>
+      <c r="T139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U139" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG139" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT139" t="inlineStr"/>
+      <c r="AW139" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX139" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215794</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>129215807</v>
+      </c>
+      <c r="B140" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>434541</v>
+      </c>
+      <c r="R140" t="n">
+        <v>6806479</v>
+      </c>
+      <c r="S140" t="n">
+        <v>10</v>
+      </c>
+      <c r="T140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U140" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT140" t="inlineStr"/>
+      <c r="AW140" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX140" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215807</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>129215808</v>
+      </c>
+      <c r="B141" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>434355</v>
+      </c>
+      <c r="R141" t="n">
+        <v>6806519</v>
+      </c>
+      <c r="S141" t="n">
+        <v>10</v>
+      </c>
+      <c r="T141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U141" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG141" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT141" t="inlineStr"/>
+      <c r="AW141" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215808</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>129215809</v>
+      </c>
+      <c r="B142" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>434843</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6806853</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215809</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>129215810</v>
+      </c>
+      <c r="B143" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>434908</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6806733</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215810</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>129215812</v>
+      </c>
+      <c r="B144" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>434922</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6806746</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215812</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>129215813</v>
+      </c>
+      <c r="B145" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>434803</v>
+      </c>
+      <c r="R145" t="n">
+        <v>6806683</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215813</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>129215751</v>
+      </c>
+      <c r="B146" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>434673</v>
+      </c>
+      <c r="R146" t="n">
+        <v>6806460</v>
+      </c>
+      <c r="S146" t="n">
+        <v>10</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215751</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>129215752</v>
+      </c>
+      <c r="B147" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>434263</v>
+      </c>
+      <c r="R147" t="n">
+        <v>6806561</v>
+      </c>
+      <c r="S147" t="n">
+        <v>10</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215752</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>129215753</v>
+      </c>
+      <c r="B148" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>434571</v>
+      </c>
+      <c r="R148" t="n">
+        <v>6806718</v>
+      </c>
+      <c r="S148" t="n">
+        <v>10</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215753</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>129215754</v>
+      </c>
+      <c r="B149" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>434774</v>
+      </c>
+      <c r="R149" t="n">
+        <v>6806803</v>
+      </c>
+      <c r="S149" t="n">
+        <v>10</v>
+      </c>
+      <c r="T149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG149" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT149" t="inlineStr"/>
+      <c r="AW149" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX149" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215754</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>129215755</v>
+      </c>
+      <c r="B150" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>434812</v>
+      </c>
+      <c r="R150" t="n">
+        <v>6806771</v>
+      </c>
+      <c r="S150" t="n">
+        <v>10</v>
+      </c>
+      <c r="T150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U150" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG150" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT150" t="inlineStr"/>
+      <c r="AW150" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX150" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215755</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>129215756</v>
+      </c>
+      <c r="B151" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>434857</v>
+      </c>
+      <c r="R151" t="n">
+        <v>6806824</v>
+      </c>
+      <c r="S151" t="n">
+        <v>10</v>
+      </c>
+      <c r="T151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U151" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT151" t="inlineStr"/>
+      <c r="AW151" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX151" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215756</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>129215757</v>
+      </c>
+      <c r="B152" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>434905</v>
+      </c>
+      <c r="R152" t="n">
+        <v>6806832</v>
+      </c>
+      <c r="S152" t="n">
+        <v>10</v>
+      </c>
+      <c r="T152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG152" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT152" t="inlineStr"/>
+      <c r="AW152" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX152" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215757</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>129215758</v>
+      </c>
+      <c r="B153" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>434928</v>
+      </c>
+      <c r="R153" t="n">
+        <v>6806794</v>
+      </c>
+      <c r="S153" t="n">
+        <v>10</v>
+      </c>
+      <c r="T153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U153" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG153" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT153" t="inlineStr"/>
+      <c r="AW153" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX153" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215758</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>129215759</v>
+      </c>
+      <c r="B154" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>434930</v>
+      </c>
+      <c r="R154" t="n">
+        <v>6806768</v>
+      </c>
+      <c r="S154" t="n">
+        <v>10</v>
+      </c>
+      <c r="T154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U154" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG154" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT154" t="inlineStr"/>
+      <c r="AW154" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX154" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215759</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>129215760</v>
+      </c>
+      <c r="B155" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>434895</v>
+      </c>
+      <c r="R155" t="n">
+        <v>6806736</v>
+      </c>
+      <c r="S155" t="n">
+        <v>10</v>
+      </c>
+      <c r="T155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG155" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT155" t="inlineStr"/>
+      <c r="AW155" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX155" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215760</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>129215761</v>
+      </c>
+      <c r="B156" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Borgbliket, Dlr</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>434924</v>
+      </c>
+      <c r="R156" t="n">
+        <v>6806749</v>
+      </c>
+      <c r="S156" t="n">
+        <v>10</v>
+      </c>
+      <c r="T156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U156" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG156" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT156" t="inlineStr"/>
+      <c r="AW156" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX156" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129215761</t>
         </is>
@@ -14640,6 +17424,29 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79514</v>
+        <v>79515</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89478</v>
+        <v>89479</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78885</v>
+        <v>78886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79239</v>
+        <v>79240</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
+          <t>Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89479</v>
+        <v>89485</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9670,7 +9670,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9787,7 +9787,7 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -14934,7 +14934,7 @@
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
@@ -24481,7 +24481,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98230</v>
+        <v>98236</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -9319,7 +9319,7 @@
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -10493,7 +10493,7 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Göran Rönning, Åke Sköld, Evalena Sköld</t>
+          <t>Evalena Sköld, Åke Sköld, Göran Rönning, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -24481,7 +24481,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98240</v>
+        <v>98242</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79517</v>
+        <v>79520</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89489</v>
+        <v>89491</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78888</v>
+        <v>78891</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79242</v>
+        <v>79245</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -18309,7 +18309,7 @@
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Åke Sköld, Elisa Andersson, Eva Löfqvist, Evalena Sköld, Göran Rönning</t>
+          <t>Åke Sköld, Göran Rönning, Evalena Sköld, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
@@ -24481,7 +24481,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98242</v>
+        <v>98244</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26234,7 +26234,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>137044520</v>
       </c>
       <c r="B3" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
         <v>137024533</v>
       </c>
       <c r="B4" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -6783,7 +6783,7 @@
         <v>137044151</v>
       </c>
       <c r="B61" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         <v>137044159</v>
       </c>
       <c r="B62" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>137044522</v>
       </c>
       <c r="B63" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>137044523</v>
       </c>
       <c r="B64" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>137044524</v>
       </c>
       <c r="B65" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         <v>137044527</v>
       </c>
       <c r="B66" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
         <v>137059445</v>
       </c>
       <c r="B67" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
         <v>137059575</v>
       </c>
       <c r="B68" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>137063588</v>
       </c>
       <c r="B69" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         <v>137064326</v>
       </c>
       <c r="B70" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7975,7 +7975,7 @@
         <v>137064327</v>
       </c>
       <c r="B71" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         <v>137064341</v>
       </c>
       <c r="B72" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         <v>137064343</v>
       </c>
       <c r="B73" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>137064345</v>
       </c>
       <c r="B74" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8443,7 +8443,7 @@
         <v>137064352</v>
       </c>
       <c r="B75" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8560,7 +8560,7 @@
         <v>137064355</v>
       </c>
       <c r="B76" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>137064357</v>
       </c>
       <c r="B77" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         <v>137064361</v>
       </c>
       <c r="B78" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8915,7 +8915,7 @@
         <v>137064362</v>
       </c>
       <c r="B79" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>137064363</v>
       </c>
       <c r="B80" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>137064365</v>
       </c>
       <c r="B81" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -12528,7 +12528,7 @@
         <v>137030265</v>
       </c>
       <c r="B113" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12649,7 +12649,7 @@
         <v>137064347</v>
       </c>
       <c r="B114" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>137064349</v>
       </c>
       <c r="B115" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12883,7 +12883,7 @@
         <v>137064360</v>
       </c>
       <c r="B116" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>137064354</v>
       </c>
       <c r="B117" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137029257</v>
       </c>
       <c r="B142" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15886,7 +15886,7 @@
         <v>137030476</v>
       </c>
       <c r="B143" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>137031483</v>
       </c>
       <c r="B144" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>137044152</v>
       </c>
       <c r="B145" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>137044153</v>
       </c>
       <c r="B146" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16385,7 +16385,7 @@
         <v>137044154</v>
       </c>
       <c r="B147" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>137044158</v>
       </c>
       <c r="B148" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>137044160</v>
       </c>
       <c r="B149" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>137044161</v>
       </c>
       <c r="B150" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16863,7 +16863,7 @@
         <v>137044506</v>
       </c>
       <c r="B151" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>137044507</v>
       </c>
       <c r="B152" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17113,7 +17113,7 @@
         <v>137044508</v>
       </c>
       <c r="B153" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>137044519</v>
       </c>
       <c r="B154" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17355,7 +17355,7 @@
         <v>137044521</v>
       </c>
       <c r="B155" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17477,7 +17477,7 @@
         <v>137044526</v>
       </c>
       <c r="B156" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>137044528</v>
       </c>
       <c r="B157" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>137044529</v>
       </c>
       <c r="B158" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>137044530</v>
       </c>
       <c r="B159" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -17960,7 +17960,7 @@
         <v>137044531</v>
       </c>
       <c r="B160" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18082,7 +18082,7 @@
         <v>137060154</v>
       </c>
       <c r="B161" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18207,7 +18207,7 @@
         <v>137060155</v>
       </c>
       <c r="B162" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18336,7 +18336,7 @@
         <v>137060176</v>
       </c>
       <c r="B163" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>137060177</v>
       </c>
       <c r="B164" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>137060179</v>
       </c>
       <c r="B165" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>137060181</v>
       </c>
       <c r="B166" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18836,7 +18836,7 @@
         <v>137060182</v>
       </c>
       <c r="B167" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>137060183</v>
       </c>
       <c r="B168" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>137060184</v>
       </c>
       <c r="B169" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19211,7 +19211,7 @@
         <v>137060185</v>
       </c>
       <c r="B170" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>137060186</v>
       </c>
       <c r="B171" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>137064356</v>
       </c>
       <c r="B176" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89506</v>
+        <v>89509</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79535</v>
+        <v>79545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89509</v>
+        <v>89519</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>137030265</v>
       </c>
       <c r="B130" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>137044198</v>
       </c>
       <c r="B131" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>137044206</v>
       </c>
       <c r="B132" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>137064347</v>
       </c>
       <c r="B133" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>137064349</v>
       </c>
       <c r="B134" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>137064360</v>
       </c>
       <c r="B135" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>137064354</v>
       </c>
       <c r="B136" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>137029257</v>
       </c>
       <c r="B161" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>137030476</v>
       </c>
       <c r="B162" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>137031483</v>
       </c>
       <c r="B163" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>137044152</v>
       </c>
       <c r="B164" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>137044153</v>
       </c>
       <c r="B165" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>137044154</v>
       </c>
       <c r="B166" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>137044158</v>
       </c>
       <c r="B167" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>137044160</v>
       </c>
       <c r="B168" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>137044161</v>
       </c>
       <c r="B169" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>137044162</v>
       </c>
       <c r="B170" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>137044165</v>
       </c>
       <c r="B171" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>137044168</v>
       </c>
       <c r="B172" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>137044169</v>
       </c>
       <c r="B173" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>137044170</v>
       </c>
       <c r="B174" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>137044171</v>
       </c>
       <c r="B175" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>137044175</v>
       </c>
       <c r="B176" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>137044177</v>
       </c>
       <c r="B177" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>137044183</v>
       </c>
       <c r="B178" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>137044184</v>
       </c>
       <c r="B179" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>137044188</v>
       </c>
       <c r="B180" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>137044189</v>
       </c>
       <c r="B181" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>137044190</v>
       </c>
       <c r="B182" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>137044191</v>
       </c>
       <c r="B183" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>137044192</v>
       </c>
       <c r="B184" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>137044196</v>
       </c>
       <c r="B185" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>137044197</v>
       </c>
       <c r="B186" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>137044203</v>
       </c>
       <c r="B187" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>137044506</v>
       </c>
       <c r="B188" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>137044507</v>
       </c>
       <c r="B189" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>137044508</v>
       </c>
       <c r="B190" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>137044519</v>
       </c>
       <c r="B191" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>137044521</v>
       </c>
       <c r="B192" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>137044526</v>
       </c>
       <c r="B193" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>137044528</v>
       </c>
       <c r="B194" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>137044529</v>
       </c>
       <c r="B195" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>137044530</v>
       </c>
       <c r="B196" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>137044531</v>
       </c>
       <c r="B197" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>137060154</v>
       </c>
       <c r="B198" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>137060155</v>
       </c>
       <c r="B199" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>137060176</v>
       </c>
       <c r="B200" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>137060177</v>
       </c>
       <c r="B201" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>137060179</v>
       </c>
       <c r="B202" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>137060181</v>
       </c>
       <c r="B203" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>137060182</v>
       </c>
       <c r="B204" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>137060183</v>
       </c>
       <c r="B205" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>137060184</v>
       </c>
       <c r="B206" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>137060185</v>
       </c>
       <c r="B207" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>137060186</v>
       </c>
       <c r="B208" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>137044182</v>
       </c>
       <c r="B212" t="n">
-        <v>56587</v>
+        <v>56597</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>137044186</v>
       </c>
       <c r="B213" t="n">
-        <v>56587</v>
+        <v>56597</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89519</v>
+        <v>89520</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Evalena Sköld, Göran Rönning, Åke Sköld, Eva Löfqvist, Elisa Andersson</t>
+          <t>Elisa Andersson, Eva Löfqvist, Åke Sköld, Göran Rönning, Evalena Sköld</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -8960,7 +8960,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Elisa Andersson, Eva Löfqvist, Åke Sköld, Göran Rönning, Evalena Sköld</t>
+          <t>Evalena Sköld, Göran Rönning, Åke Sköld, Eva Löfqvist, Elisa Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79545</v>
+        <v>79548</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89520</v>
+        <v>89523</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>137030265</v>
       </c>
       <c r="B130" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>137044198</v>
       </c>
       <c r="B131" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>137044206</v>
       </c>
       <c r="B132" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>137064347</v>
       </c>
       <c r="B133" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>137064349</v>
       </c>
       <c r="B134" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>137064360</v>
       </c>
       <c r="B135" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>137064354</v>
       </c>
       <c r="B136" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>137029257</v>
       </c>
       <c r="B161" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>137030476</v>
       </c>
       <c r="B162" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>137031483</v>
       </c>
       <c r="B163" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>137044152</v>
       </c>
       <c r="B164" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>137044153</v>
       </c>
       <c r="B165" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>137044154</v>
       </c>
       <c r="B166" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>137044158</v>
       </c>
       <c r="B167" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>137044160</v>
       </c>
       <c r="B168" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>137044161</v>
       </c>
       <c r="B169" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>137044162</v>
       </c>
       <c r="B170" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>137044165</v>
       </c>
       <c r="B171" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>137044168</v>
       </c>
       <c r="B172" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>137044169</v>
       </c>
       <c r="B173" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>137044170</v>
       </c>
       <c r="B174" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>137044171</v>
       </c>
       <c r="B175" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>137044175</v>
       </c>
       <c r="B176" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>137044177</v>
       </c>
       <c r="B177" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>137044183</v>
       </c>
       <c r="B178" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>137044184</v>
       </c>
       <c r="B179" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>137044188</v>
       </c>
       <c r="B180" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>137044189</v>
       </c>
       <c r="B181" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>137044190</v>
       </c>
       <c r="B182" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>137044191</v>
       </c>
       <c r="B183" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>137044192</v>
       </c>
       <c r="B184" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>137044196</v>
       </c>
       <c r="B185" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>137044197</v>
       </c>
       <c r="B186" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>137044203</v>
       </c>
       <c r="B187" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>137044506</v>
       </c>
       <c r="B188" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>137044507</v>
       </c>
       <c r="B189" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>137044508</v>
       </c>
       <c r="B190" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>137044519</v>
       </c>
       <c r="B191" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>137044521</v>
       </c>
       <c r="B192" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>137044526</v>
       </c>
       <c r="B193" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>137044528</v>
       </c>
       <c r="B194" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>137044529</v>
       </c>
       <c r="B195" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>137044530</v>
       </c>
       <c r="B196" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>137044531</v>
       </c>
       <c r="B197" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>137060154</v>
       </c>
       <c r="B198" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>137060155</v>
       </c>
       <c r="B199" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>137060176</v>
       </c>
       <c r="B200" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>137060177</v>
       </c>
       <c r="B201" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>137060179</v>
       </c>
       <c r="B202" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>137060181</v>
       </c>
       <c r="B203" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>137060182</v>
       </c>
       <c r="B204" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>137060183</v>
       </c>
       <c r="B205" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>137060184</v>
       </c>
       <c r="B206" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>137060185</v>
       </c>
       <c r="B207" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>137060186</v>
       </c>
       <c r="B208" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>137044182</v>
       </c>
       <c r="B212" t="n">
-        <v>56597</v>
+        <v>56598</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>137044186</v>
       </c>
       <c r="B213" t="n">
-        <v>56597</v>
+        <v>56598</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79548</v>
+        <v>79553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89523</v>
+        <v>89528</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>137030265</v>
       </c>
       <c r="B130" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>137044198</v>
       </c>
       <c r="B131" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>137044206</v>
       </c>
       <c r="B132" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>137064347</v>
       </c>
       <c r="B133" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>137064349</v>
       </c>
       <c r="B134" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>137064360</v>
       </c>
       <c r="B135" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>137064354</v>
       </c>
       <c r="B136" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79553</v>
+        <v>79564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89528</v>
+        <v>89539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79564</v>
+        <v>79565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89539</v>
+        <v>89540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79565</v>
+        <v>79567</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89540</v>
+        <v>89543</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>

--- a/artfynd/A 43867-2025 artfynd.xlsx
+++ b/artfynd/A 43867-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137044180</v>
       </c>
       <c r="B2" t="n">
-        <v>79567</v>
+        <v>79571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>137044172</v>
       </c>
       <c r="B4" t="n">
-        <v>89543</v>
+        <v>89547</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>137044520</v>
       </c>
       <c r="B5" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
         <v>137024533</v>
       </c>
       <c r="B6" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>137044151</v>
       </c>
       <c r="B63" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>137044159</v>
       </c>
       <c r="B64" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>137044163</v>
       </c>
       <c r="B65" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>137044164</v>
       </c>
       <c r="B66" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         <v>137044166</v>
       </c>
       <c r="B67" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7582,7 +7582,7 @@
         <v>137044167</v>
       </c>
       <c r="B68" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7694,7 +7694,7 @@
         <v>137044178</v>
       </c>
       <c r="B69" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         <v>137044181</v>
       </c>
       <c r="B70" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7918,7 +7918,7 @@
         <v>137044193</v>
       </c>
       <c r="B71" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8030,7 +8030,7 @@
         <v>137044199</v>
       </c>
       <c r="B72" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>137044204</v>
       </c>
       <c r="B73" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8254,7 +8254,7 @@
         <v>137044205</v>
       </c>
       <c r="B74" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         <v>137044522</v>
       </c>
       <c r="B75" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8488,7 +8488,7 @@
         <v>137044523</v>
       </c>
       <c r="B76" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8610,7 +8610,7 @@
         <v>137044524</v>
       </c>
       <c r="B77" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>137044527</v>
       </c>
       <c r="B78" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8854,7 +8854,7 @@
         <v>137059445</v>
       </c>
       <c r="B79" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8975,7 +8975,7 @@
         <v>137059575</v>
       </c>
       <c r="B80" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9096,7 +9096,7 @@
         <v>137063588</v>
       </c>
       <c r="B81" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9217,7 +9217,7 @@
         <v>137064326</v>
       </c>
       <c r="B82" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9334,7 +9334,7 @@
         <v>137064327</v>
       </c>
       <c r="B83" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
         <v>137064341</v>
       </c>
       <c r="B84" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>137064343</v>
       </c>
       <c r="B85" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>137064345</v>
       </c>
       <c r="B86" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>137064352</v>
       </c>
       <c r="B87" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9919,7 +9919,7 @@
         <v>137064355</v>
       </c>
       <c r="B88" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
         <v>137064357</v>
       </c>
       <c r="B89" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>137064361</v>
       </c>
       <c r="B90" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         <v>137064362</v>
       </c>
       <c r="B91" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>137064363</v>
       </c>
       <c r="B92" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>137064365</v>
       </c>
       <c r="B93" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10625,7 +10625,7 @@
         <v>137044202</v>
       </c>
       <c r="B94" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>137044194</v>
       </c>
       <c r="B101" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11485,7 +11485,7 @@
         <v>137044200</v>
       </c>
       <c r="B102" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>137044195</v>
       </c>
       <c r="B117" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13155,7 +13155,7 @@
         <v>137044201</v>
       </c>
       <c r="B118" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14477,7 +14477,7 @@
         <v>137030265</v>
       </c>
       <c r="B130" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>137044198</v>
       </c>
       <c r="B131" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14707,7 +14707,7 @@
         <v>137044206</v>
       </c>
       <c r="B132" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14820,7 +14820,7 @@
         <v>137064347</v>
       </c>
       <c r="B133" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>137064349</v>
       </c>
       <c r="B134" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>137064360</v>
       </c>
       <c r="B135" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>137064354</v>
       </c>
       <c r="B136" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>137029257</v>
       </c>
       <c r="B161" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>137030476</v>
       </c>
       <c r="B162" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18182,7 +18182,7 @@
         <v>137031483</v>
       </c>
       <c r="B163" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18304,7 +18304,7 @@
         <v>137044152</v>
       </c>
       <c r="B164" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>137044153</v>
       </c>
       <c r="B165" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>137044154</v>
       </c>
       <c r="B166" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18653,7 +18653,7 @@
         <v>137044158</v>
       </c>
       <c r="B167" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>137044160</v>
       </c>
       <c r="B168" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18884,7 +18884,7 @@
         <v>137044161</v>
       </c>
       <c r="B169" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>137044162</v>
       </c>
       <c r="B170" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>137044165</v>
       </c>
       <c r="B171" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19241,7 +19241,7 @@
         <v>137044168</v>
       </c>
       <c r="B172" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>137044169</v>
       </c>
       <c r="B173" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>137044170</v>
       </c>
       <c r="B174" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>137044171</v>
       </c>
       <c r="B175" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>137044175</v>
       </c>
       <c r="B176" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>137044177</v>
       </c>
       <c r="B177" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -19934,7 +19934,7 @@
         <v>137044183</v>
       </c>
       <c r="B178" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>137044184</v>
       </c>
       <c r="B179" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -20165,7 +20165,7 @@
         <v>137044188</v>
       </c>
       <c r="B180" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -20278,7 +20278,7 @@
         <v>137044189</v>
       </c>
       <c r="B181" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -20396,7 +20396,7 @@
         <v>137044190</v>
       </c>
       <c r="B182" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20517,7 +20517,7 @@
         <v>137044191</v>
       </c>
       <c r="B183" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>137044192</v>
       </c>
       <c r="B184" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         <v>137044196</v>
       </c>
       <c r="B185" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -20869,7 +20869,7 @@
         <v>137044197</v>
       </c>
       <c r="B186" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -20982,7 +20982,7 @@
         <v>137044203</v>
       </c>
       <c r="B187" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>137044506</v>
       </c>
       <c r="B188" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>137044507</v>
       </c>
       <c r="B189" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>137044508</v>
       </c>
       <c r="B190" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -21458,7 +21458,7 @@
         <v>137044519</v>
       </c>
       <c r="B191" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>137044521</v>
       </c>
       <c r="B192" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>137044526</v>
       </c>
       <c r="B193" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>137044528</v>
       </c>
       <c r="B194" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>137044529</v>
       </c>
       <c r="B195" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -22043,7 +22043,7 @@
         <v>137044530</v>
       </c>
       <c r="B196" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -22161,7 +22161,7 @@
         <v>137044531</v>
       </c>
       <c r="B197" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>137060154</v>
       </c>
       <c r="B198" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>137060155</v>
       </c>
       <c r="B199" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>137060176</v>
       </c>
       <c r="B200" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>137060177</v>
       </c>
       <c r="B201" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>137060179</v>
       </c>
       <c r="B202" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>137060181</v>
       </c>
       <c r="B203" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
         <v>137060182</v>
       </c>
       <c r="B204" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23126,7 +23126,7 @@
         <v>137060183</v>
       </c>
       <c r="B205" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23247,7 +23247,7 @@
         <v>137060184</v>
       </c>
       <c r="B206" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23368,7 +23368,7 @@
         <v>137060185</v>
       </c>
       <c r="B207" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>137060186</v>
       </c>
       <c r="B208" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23940,7 +23940,7 @@
         <v>137044182</v>
       </c>
       <c r="B212" t="n">
-        <v>56598</v>
+        <v>56601</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24053,7 +24053,7 @@
         <v>137044186</v>
       </c>
       <c r="B213" t="n">
-        <v>56598</v>
+        <v>56601</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>137064356</v>
       </c>
       <c r="B215" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>137044173</v>
       </c>
       <c r="B232" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
